--- a/artfynd/A 47084-2025 artfynd.xlsx
+++ b/artfynd/A 47084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129274117</v>
       </c>
       <c r="B2" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129274118</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47084-2025 artfynd.xlsx
+++ b/artfynd/A 47084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129274117</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129274118</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47084-2025 artfynd.xlsx
+++ b/artfynd/A 47084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129274117</v>
       </c>
       <c r="B2" t="n">
-        <v>97627</v>
+        <v>97639</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129274118</v>
       </c>
       <c r="B3" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47084-2025 artfynd.xlsx
+++ b/artfynd/A 47084-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129274117</v>
       </c>
       <c r="B2" t="n">
-        <v>97639</v>
+        <v>97640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129274118</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
